--- a/public/samples/spws/hoop.xlsx
+++ b/public/samples/spws/hoop.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leanhtu/Desktop/merge/project_freelance/KHO/kho SPW/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2018EC-A890-E34D-8EB9-7EC6AD681DCC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15440" xr2:uid="{01FB8B9F-56C6-3F43-84C9-FF0D7E9C8395}"/>
+    <workbookView windowWidth="28800" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="53">
   <si>
     <t>Tồn</t>
   </si>
@@ -58,6 +47,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
   </si>
   <si>
     <t>H 2 025</t>
@@ -186,31 +178,372 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
-    <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+    <numFmt numFmtId="178" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -218,29 +551,315 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -289,7 +908,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -322,26 +941,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -374,23 +976,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -532,21 +1117,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EB355F-500C-A04A-A665-E43E5B559325}">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.8"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="3:11">
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="G1" s="3"/>
@@ -555,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -592,13 +1172,16 @@
       <c r="L2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>2.5</v>
@@ -610,13 +1193,13 @@
         <v>19</v>
       </c>
       <c r="G3" s="3">
-        <v>30.400000000000002</v>
+        <v>30.4</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3">
@@ -626,12 +1209,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1">
         <v>3.2</v>
@@ -646,10 +1229,10 @@
         <v>146</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4">
@@ -659,12 +1242,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>4.5</v>
@@ -676,13 +1259,13 @@
         <v>90</v>
       </c>
       <c r="G5" s="3">
-        <v>251.99999999999997</v>
+        <v>252</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5">
@@ -692,12 +1275,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>4.5</v>
@@ -709,13 +1292,13 @@
         <v>96</v>
       </c>
       <c r="G6" s="3">
-        <v>268.79999999999995</v>
+        <v>268.8</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6">
@@ -725,12 +1308,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1">
         <v>6.4</v>
@@ -745,10 +1328,10 @@
         <v>516</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7">
@@ -758,12 +1341,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1">
         <v>6.4</v>
@@ -778,10 +1361,10 @@
         <v>129</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8">
@@ -791,12 +1374,12 @@
         <v>124.7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
         <v>4.5</v>
@@ -811,10 +1394,10 @@
         <v>520</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9">
@@ -824,45 +1407,45 @@
         <v>520</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1">
         <v>3.2</v>
       </c>
       <c r="D10" s="2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="F10">
         <v>56</v>
       </c>
       <c r="G10" s="3">
-        <v>123.20000000000002</v>
+        <v>123.2</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10">
         <v>54</v>
       </c>
       <c r="L10" s="3">
-        <v>118.80000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
       </c>
       <c r="C11" s="1">
         <v>4.5</v>
@@ -877,10 +1460,10 @@
         <v>72.8</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11">
@@ -890,12 +1473,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1">
         <v>6.4</v>
@@ -910,10 +1493,10 @@
         <v>108</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12">
@@ -923,12 +1506,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1">
         <v>4.5</v>
@@ -943,10 +1526,10 @@
         <v>400</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13">
@@ -956,30 +1539,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1">
         <v>4.5</v>
       </c>
       <c r="D14" s="2">
-        <v>16.600000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="F14">
         <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>132.80000000000001</v>
+        <v>132.8</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14">
@@ -989,12 +1572,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1">
         <v>4.5</v>
@@ -1009,10 +1592,10 @@
         <v>162</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15">
@@ -1022,12 +1605,12 @@
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1">
         <v>4.5</v>
@@ -1042,10 +1625,10 @@
         <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16">
@@ -1055,30 +1638,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1">
         <v>4.5</v>
       </c>
       <c r="D17" s="2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="F17">
         <v>16</v>
       </c>
       <c r="G17" s="3">
-        <v>35.200000000000003</v>
+        <v>35.2</v>
       </c>
       <c r="H17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17">
@@ -1088,12 +1671,12 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1">
         <v>4.5</v>
@@ -1108,10 +1691,10 @@
         <v>54</v>
       </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18">
@@ -1121,12 +1704,12 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1">
         <v>4.5</v>
@@ -1141,10 +1724,10 @@
         <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19">
@@ -1154,12 +1737,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" s="1">
         <v>7.2</v>
@@ -1174,10 +1757,10 @@
         <v>531</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20">
@@ -1187,12 +1770,12 @@
         <v>531</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" s="1">
         <v>7.2</v>
@@ -1204,28 +1787,28 @@
         <v>7</v>
       </c>
       <c r="G21" s="3">
-        <v>26.599999999999998</v>
+        <v>26.6</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21">
         <v>7</v>
       </c>
       <c r="L21" s="3">
-        <v>26.599999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
         <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
       </c>
       <c r="C22" s="1">
         <v>4.5</v>
@@ -1240,10 +1823,10 @@
         <v>22</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22">
@@ -1253,12 +1836,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1">
         <v>4.5</v>
@@ -1270,13 +1853,13 @@
         <v>180</v>
       </c>
       <c r="G23" s="3">
-        <v>503.99999999999994</v>
+        <v>504</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23">
@@ -1286,12 +1869,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1">
         <v>7.2</v>
@@ -1306,10 +1889,10 @@
         <v>49.5</v>
       </c>
       <c r="H24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J24" s="5">
         <v>44573</v>
@@ -1321,12 +1904,12 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
         <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
       </c>
       <c r="C25" s="1">
         <v>4.5</v>
@@ -1338,13 +1921,13 @@
         <v>73</v>
       </c>
       <c r="G25" s="3">
-        <v>197.10000000000002</v>
+        <v>197.1</v>
       </c>
       <c r="H25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J25" s="5">
         <v>44701</v>
@@ -1356,12 +1939,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
         <v>4.5</v>
@@ -1376,10 +1959,10 @@
         <v>540</v>
       </c>
       <c r="H26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J26" s="5">
         <v>44708</v>
@@ -1391,12 +1974,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
       </c>
       <c r="C27" s="1">
         <v>4.5</v>
@@ -1411,10 +1994,10 @@
         <v>540</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="5">
         <v>44708</v>
@@ -1426,12 +2009,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1">
         <v>3.2</v>
@@ -1446,10 +2029,10 @@
         <v>200</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="5">
         <v>44708</v>
@@ -1461,12 +2044,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1">
         <v>8</v>
@@ -1481,10 +2064,10 @@
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J29" s="5">
         <v>44750</v>
@@ -1496,12 +2079,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -1516,10 +2099,10 @@
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" s="5">
         <v>44750</v>
@@ -1531,12 +2114,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" s="1">
         <v>4.5</v>
@@ -1551,10 +2134,10 @@
         <v>2010</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J31" s="5">
         <v>44750</v>
@@ -1566,12 +2149,12 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s">
         <v>25</v>
-      </c>
-      <c r="B32" t="s">
-        <v>24</v>
       </c>
       <c r="C32" s="1">
         <v>4.5</v>
@@ -1586,10 +2169,10 @@
         <v>2010</v>
       </c>
       <c r="H32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J32" s="5">
         <v>44750</v>
@@ -1601,12 +2184,12 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C33" s="1">
         <v>4.5</v>
@@ -1621,10 +2204,10 @@
         <v>180</v>
       </c>
       <c r="H33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J33" s="5">
         <v>44750</v>
@@ -1636,30 +2219,30 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C34" s="1">
         <v>4.5</v>
       </c>
       <c r="D34" s="2">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="F34">
         <v>120</v>
       </c>
       <c r="G34" s="3">
-        <v>491.99999999999994</v>
+        <v>492</v>
       </c>
       <c r="H34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J34" s="5">
         <v>44750</v>
@@ -1668,21 +2251,21 @@
         <v>120</v>
       </c>
       <c r="L34" s="3">
-        <v>491.99999999999994</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1">
         <v>3.2</v>
       </c>
       <c r="D35" s="2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="F35">
         <v>80</v>
@@ -1691,10 +2274,10 @@
         <v>176</v>
       </c>
       <c r="H35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J35" s="5">
         <v>44750</v>
@@ -1708,5 +2291,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>